--- a/Result/profitability/2405.xlsx
+++ b/Result/profitability/2405.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.18</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.007499999999999986</v>
+        <v>-0.002499999999999988</v>
       </c>
       <c r="N2" t="n">
-        <v>38.8975</v>
+        <v>39.10375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.02</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.002499999999999985</v>
+        <v>0.002500000000000013</v>
       </c>
       <c r="N3" t="n">
-        <v>37.78625</v>
+        <v>37.74124999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003750000000000014</v>
+        <v>0.005000000000000013</v>
       </c>
       <c r="N4" t="n">
-        <v>35.9725</v>
+        <v>36.09375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0.007500000000000014</v>
+        <v>0.03000000000000002</v>
       </c>
       <c r="N5" t="n">
-        <v>35.08</v>
+        <v>35.13</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02375000000000001</v>
+        <v>0.02625000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>33.26125</v>
+        <v>33.6675</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03749999999999998</v>
+        <v>-0.02874999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>31.64125</v>
+        <v>33.35375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.52</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.09624999999999999</v>
+        <v>-0.09374999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>31.115</v>
+        <v>30.6875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9832,6 +9832,135 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2405</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>481</v>
+      </c>
+      <c r="D75" t="n">
+        <v>282</v>
+      </c>
+      <c r="E75" t="n">
+        <v>200</v>
+      </c>
+      <c r="F75" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="G75" t="n">
+        <v>6</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.19%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>8</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.02749999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.48625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.420000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.07611840640997114</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.125</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.009729992702505408</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
